--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jevans8\Repos\lsip_dashboard\Data\3-2_dataText\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-2_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5FC4C16-EB78-4779-978A-367C83BDA8EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313AEEE4-01DB-42B3-A471-38C5A343E7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33720" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
   <sheets>
     <sheet name="dataText" sheetId="1" r:id="rId1"/>
@@ -706,9 +706,6 @@
     <t>Growth from 2024 to 2035</t>
   </si>
   <si>
-    <t>July 2025 data</t>
-  </si>
-  <si>
     <t>Growth from 2024 to 2035. The LSIP boundaries have changed and new CAs have been created since this data was published so some areas no longer have data</t>
   </si>
   <si>
@@ -746,9 +743,6 @@
   </si>
   <si>
     <t>Jul 2024 - Jun 2025</t>
-  </si>
-  <si>
-    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts so the latest data available covers up to July 2025. More up to date data on new adverts is still available directly from the  &lt;a href="https://www.ons.gov.uk/employmentandlabourmarket/peopleinwork/employmentandemployeetypes/datasets/labourdemandvolumesbystandardoccupationclassificationsoc2020uk"&gt;ONS website&lt;/a&gt;.</t>
   </si>
   <si>
     <t>Dec 2023 - Dec 2024 data</t>
@@ -811,6 +805,12 @@
 &lt;li&gt;Use caution when interpreting this data. A difference between subgroups does not necessarily imply any causality. There could be other contributing factors at work.&lt;/li&gt;
 &lt;li&gt;Figures for newly formed CAs have been calculated from Local Authority data to create a back series. There may be small differences to the published data for these geographies due to rounding errors.&lt;/li&gt;
 &lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t>November 2025 data</t>
+  </si>
+  <si>
+    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. ONS have partially imputed the data for October and November 2025 due to their source presenting a larger level of duplicate adverts not being identified as such. The adjustment has been calculated based on the average trend of the source data for the past year. As such, month-on-month trends during this period should be treated with caution.</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1293,7 @@
         <v>152</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -1334,7 +1334,7 @@
         <v>154</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>22</v>
@@ -1375,7 +1375,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>22</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>22</v>
@@ -1457,7 +1457,7 @@
         <v>153</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>22</v>
@@ -1498,7 +1498,7 @@
         <v>156</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>22</v>
@@ -1539,7 +1539,7 @@
         <v>157</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>22</v>
@@ -1580,7 +1580,7 @@
         <v>158</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
@@ -1621,10 +1621,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>199</v>
+        <v>218</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>168</v>
@@ -1662,7 +1662,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>23</v>
@@ -1703,7 +1703,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>23</v>
@@ -1744,7 +1744,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>23</v>
@@ -1785,19 +1785,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="D14" t="s">
+        <v>213</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>39</v>
@@ -1826,19 +1826,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>40</v>
@@ -1867,19 +1867,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D16" t="s">
+        <v>213</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D16" t="s">
-        <v>215</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>212</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>41</v>
@@ -1908,19 +1908,19 @@
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D17" t="s">
+        <v>213</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D17" t="s">
-        <v>215</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>42</v>
@@ -2034,13 +2034,13 @@
         <v>192</v>
       </c>
       <c r="C20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>194</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>150</v>
@@ -2075,16 +2075,16 @@
         <v>192</v>
       </c>
       <c r="C21" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>195</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>45</v>
@@ -2113,7 +2113,7 @@
         <v>159</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-2_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{313AEEE4-01DB-42B3-A471-38C5A343E7C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401B9959-841B-4BE2-9867-042A5800898B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -810,7 +810,7 @@
     <t>November 2025 data</t>
   </si>
   <si>
-    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. ONS have partially imputed the data for October and November 2025 due to their source presenting a larger level of duplicate adverts not being identified as such. The adjustment has been calculated based on the average trend of the source data for the past year. As such, month-on-month trends during this period should be treated with caution.</t>
+    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. The adjustment applied to the data has been calculated based on the average trend of the source data for the past year. As such, month-on-month trends during the affected period should be treated with caution.</t>
   </si>
 </sst>
 </file>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-2_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401B9959-841B-4BE2-9867-042A5800898B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACF0384-2D52-4FE0-B51C-D7107E9E5262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -810,7 +810,7 @@
     <t>November 2025 data</t>
   </si>
   <si>
-    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. The adjustment applied to the data has been calculated based on the average trend of the source data for the past year. As such, month-on-month trends during the affected period should be treated with caution.</t>
+    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. ONS suppressed some of the data in June and July 2025 due to quality concerns. As a result, the sum of new adverts across all SOCs may not equal the England total. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution.</t>
   </si>
 </sst>
 </file>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-2_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AACF0384-2D52-4FE0-B51C-D7107E9E5262}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38193FE4-DC94-4679-8579-1C9A195E03C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -810,7 +810,7 @@
     <t>November 2025 data</t>
   </si>
   <si>
-    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. ONS suppressed some of the data in June and July 2025 due to quality concerns. As a result, the sum of new adverts across all SOCs may not equal the England total. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution.</t>
+    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. ONS have suppressed some of the data in June and July 2025 due to quality concerns. This has resulted in a drop in numbers over the months that include June and July 2025 in their rolling average calculation. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution.</t>
   </si>
 </sst>
 </file>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-2_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38193FE4-DC94-4679-8579-1C9A195E03C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E80AAA4-229A-4894-A01C-A64D6313197E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -810,7 +810,7 @@
     <t>November 2025 data</t>
   </si>
   <si>
-    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. ONS have suppressed some of the data in June and July 2025 due to quality concerns. This has resulted in a drop in numbers over the months that include June and July 2025 in their rolling average calculation. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution.</t>
+    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occured, only the unsuppressed data is included in the rolling average. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution.</t>
   </si>
 </sst>
 </file>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-2_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E80AAA4-229A-4894-A01C-A64D6313197E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3775556D-A6CF-46C1-85D4-568CAADE983A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -810,7 +810,7 @@
     <t>November 2025 data</t>
   </si>
   <si>
-    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occured, only the unsuppressed data is included in the rolling average. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution.</t>
+    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution.</t>
   </si>
 </sst>
 </file>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-2_dataText\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjames2\OneDrive - Department for Education\Documents\RProjects\lsip_dashboard\Data\3-2_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3775556D-A6CF-46C1-85D4-568CAADE983A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0345C9C8-3A9A-4897-A1A7-2193E943457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
+    <workbookView xWindow="760" yWindow="740" windowWidth="20660" windowHeight="14300" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
   <sheets>
     <sheet name="dataText" sheetId="1" r:id="rId1"/>
@@ -742,9 +742,6 @@
 Unknown (activity not captured): The student was not found to have any participation in education, apprenticeship or employment nor recorded as receiving out-of-work benefits at any point in the year. This also includes not being recorded by their Local Authority as NEET (not engaged in education, employment or training).</t>
   </si>
   <si>
-    <t>Jul 2024 - Jun 2025</t>
-  </si>
-  <si>
     <t>Dec 2023 - Dec 2024 data</t>
   </si>
   <si>
@@ -811,6 +808,9 @@
   </si>
   <si>
     <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution.</t>
+  </si>
+  <si>
+    <t>Oct 2024 - Sep 2025</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1293,7 @@
         <v>152</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -1334,7 +1334,7 @@
         <v>154</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>22</v>
@@ -1375,7 +1375,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>22</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>22</v>
@@ -1457,7 +1457,7 @@
         <v>153</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>22</v>
@@ -1498,7 +1498,7 @@
         <v>156</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>22</v>
@@ -1539,7 +1539,7 @@
         <v>157</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>22</v>
@@ -1580,7 +1580,7 @@
         <v>158</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
@@ -1621,10 +1621,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>218</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>219</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>168</v>
@@ -1703,7 +1703,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>23</v>
@@ -1744,7 +1744,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>23</v>
@@ -1785,19 +1785,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" t="s">
+        <v>212</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D14" t="s">
-        <v>213</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>210</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>39</v>
@@ -1826,19 +1826,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>208</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>209</v>
-      </c>
       <c r="D15" t="s">
+        <v>212</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>40</v>
@@ -1867,19 +1867,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D16" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>41</v>
@@ -1908,19 +1908,19 @@
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D17" t="s">
         <v>212</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>214</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>42</v>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pjames2\OneDrive - Department for Education\Documents\RProjects\lsip_dashboard\Data\3-2_dataText\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0345C9C8-3A9A-4897-A1A7-2193E943457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{0345C9C8-3A9A-4897-A1A7-2193E943457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAD08929-B9C6-4654-8183-141C0F392468}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="740" windowWidth="20660" windowHeight="14300" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
   <sheets>
     <sheet name="dataText" sheetId="1" r:id="rId1"/>
@@ -560,9 +560,6 @@
     <t>employment volume share</t>
   </si>
   <si>
-    <t>&lt;a href='https://explore-education-statistics.service.gov.uk/data-catalogue/further-education-and-skills/2022-23'&gt;Individualised Learner Record&lt;/a&gt;</t>
-  </si>
-  <si>
     <t>&lt;ol&gt;
   &lt;li&gt;Figures are for 16-64 year olds.&lt;/li&gt;
 &lt;li&gt;Each estimate from the Annual Population Survey carries a margin of error. These are available in the original data via NOMIS. Large margins of error are usually associated with groups with only a small number of respondents. Therefore, please take caution when interpreting data from small subgroups.&lt;/li&gt;
@@ -686,9 +683,6 @@
     <t>AY22/23 data</t>
   </si>
   <si>
-    <t>&lt;a href = 'https://explore-education-statistics.service.gov.uk/find-statistics/key-stage-4-destination-measures/2022-23'&gt;Key stage 4 destination measures&lt;/a&gt;</t>
-  </si>
-  <si>
     <t>&lt;a href = 'https://explore-education-statistics.service.gov.uk/find-statistics/16-18-destination-measures'&gt;16-18 destination measures&lt;/a&gt;</t>
   </si>
   <si>
@@ -811,6 +805,12 @@
   </si>
   <si>
     <t>Oct 2024 - Sep 2025</t>
+  </si>
+  <si>
+    <t>&lt;a href = 'https://explore-education-statistics.service.gov.uk/find-statistics/key-stage-4-destination-measures/2023-24'&gt;Key stage 4 destination measures&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://explore-education-statistics.service.gov.uk/find-statistics/further-education-and-skills/2024-25'&gt;Individualised Learner Record&lt;/a&gt;</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1293,7 @@
         <v>152</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -1302,10 +1302,10 @@
         <v>19</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>28</v>
@@ -1334,7 +1334,7 @@
         <v>154</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>22</v>
@@ -1343,10 +1343,10 @@
         <v>19</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>29</v>
@@ -1375,7 +1375,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>22</v>
@@ -1384,10 +1384,10 @@
         <v>19</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>30</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>22</v>
@@ -1425,10 +1425,10 @@
         <v>19</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>31</v>
@@ -1457,7 +1457,7 @@
         <v>153</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>22</v>
@@ -1466,10 +1466,10 @@
         <v>19</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>1</v>
@@ -1498,7 +1498,7 @@
         <v>156</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>22</v>
@@ -1507,10 +1507,10 @@
         <v>19</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>32</v>
@@ -1539,7 +1539,7 @@
         <v>157</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>22</v>
@@ -1548,10 +1548,10 @@
         <v>19</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>33</v>
@@ -1580,7 +1580,7 @@
         <v>158</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
@@ -1589,10 +1589,10 @@
         <v>19</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>34</v>
@@ -1621,19 +1621,19 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>22</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>35</v>
@@ -1642,7 +1642,7 @@
         <v>135</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J10" s="8" t="s">
         <v>79</v>
@@ -1662,7 +1662,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>23</v>
@@ -1703,7 +1703,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>23</v>
@@ -1744,7 +1744,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>23</v>
@@ -1785,19 +1785,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="D14" t="s">
+        <v>210</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>39</v>
@@ -1806,7 +1806,7 @@
         <v>139</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J14" s="8" t="s">
         <v>95</v>
@@ -1826,19 +1826,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E15" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>40</v>
@@ -1847,7 +1847,7 @@
         <v>140</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J15" s="8" t="s">
         <v>98</v>
@@ -1867,19 +1867,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D16" t="s">
+        <v>210</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="D16" t="s">
-        <v>212</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>41</v>
@@ -1888,7 +1888,7 @@
         <v>141</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J16" s="8" t="s">
         <v>101</v>
@@ -1908,19 +1908,19 @@
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D17" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="D17" t="s">
-        <v>212</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>215</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>42</v>
@@ -1929,7 +1929,7 @@
         <v>142</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>104</v>
@@ -1949,10 +1949,10 @@
         <v>160</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>19</v>
@@ -1961,7 +1961,7 @@
         <v>22</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>43</v>
@@ -1970,7 +1970,7 @@
         <v>143</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>107</v>
@@ -1987,13 +1987,13 @@
     </row>
     <row r="19" spans="1:13" ht="290.5" thickBot="1">
       <c r="A19" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>19</v>
@@ -2002,28 +2002,28 @@
         <v>22</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G19" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="H19" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="I19" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="J19" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="I19" s="8" t="s">
-        <v>186</v>
-      </c>
-      <c r="J19" s="8" t="s">
+      <c r="K19" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="L19" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="L19" s="8" t="s">
+      <c r="M19" s="8" t="s">
         <v>174</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="263" thickBot="1">
@@ -2031,16 +2031,16 @@
         <v>12</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C20" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>150</v>
@@ -2072,19 +2072,19 @@
         <v>13</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C21" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>45</v>
@@ -2113,7 +2113,7 @@
         <v>159</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -2122,10 +2122,10 @@
         <v>151</v>
       </c>
       <c r="E22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G22" s="8" t="s">
         <v>124</v>
@@ -2137,7 +2137,7 @@
         <v>64</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>125</v>
@@ -2152,13 +2152,13 @@
         <v>8</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>219</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>18</v>
@@ -2173,13 +2173,13 @@
         <v>11</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>166</v>
+        <v>219</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>18</v>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{0345C9C8-3A9A-4897-A1A7-2193E943457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAD08929-B9C6-4654-8183-141C0F392468}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{0345C9C8-3A9A-4897-A1A7-2193E943457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC85E033-37C2-433B-AF55-45A2CA514156}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -798,12 +798,6 @@
 &lt;/ol&gt;</t>
   </si>
   <si>
-    <t>November 2025 data</t>
-  </si>
-  <si>
-    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution.</t>
-  </si>
-  <si>
     <t>Oct 2024 - Sep 2025</t>
   </si>
   <si>
@@ -811,6 +805,12 @@
   </si>
   <si>
     <t>&lt;a href='https://explore-education-statistics.service.gov.uk/find-statistics/further-education-and-skills/2024-25'&gt;Individualised Learner Record&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>January 2026 data</t>
+  </si>
+  <si>
+    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 data, and so some data has been supressed in this month.</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1293,7 @@
         <v>152</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -1334,7 +1334,7 @@
         <v>154</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>22</v>
@@ -1375,7 +1375,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>22</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>22</v>
@@ -1457,7 +1457,7 @@
         <v>153</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>22</v>
@@ -1498,7 +1498,7 @@
         <v>156</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>22</v>
@@ -1539,7 +1539,7 @@
         <v>157</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>22</v>
@@ -1580,7 +1580,7 @@
         <v>158</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
@@ -1621,10 +1621,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>167</v>
@@ -2037,7 +2037,7 @@
         <v>199</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>202</v>
@@ -2158,7 +2158,7 @@
         <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>18</v>
@@ -2179,7 +2179,7 @@
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>18</v>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-2_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{0345C9C8-3A9A-4897-A1A7-2193E943457D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CC85E033-37C2-433B-AF55-45A2CA514156}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E367728-AE76-4C66-AEF8-A80D4CD0BC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
   <sheets>
     <sheet name="dataText" sheetId="1" r:id="rId1"/>
@@ -807,10 +807,10 @@
     <t>&lt;a href='https://explore-education-statistics.service.gov.uk/find-statistics/further-education-and-skills/2024-25'&gt;Individualised Learner Record&lt;/a&gt;</t>
   </si>
   <si>
-    <t>January 2026 data</t>
-  </si>
-  <si>
-    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data for October and November 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 data, and so some data has been supressed in this month.</t>
+    <t>February 2026 data</t>
+  </si>
+  <si>
+    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data since October 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 and February 2026 data, and so some data has been supressed in these months.</t>
   </si>
 </sst>
 </file>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-2_dataText\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E367728-AE76-4C66-AEF8-A80D4CD0BC97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -810,7 +810,7 @@
     <t>February 2026 data</t>
   </si>
   <si>
-    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data since October 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 and February 2026 data, and so some data has been supressed in these months.</t>
+    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data since October 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 and February 2026 data, and so some data has been suppressed in these months.</t>
   </si>
 </sst>
 </file>
@@ -2193,5 +2193,15 @@
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL - FOR PUBLIC RELEASE&amp;1#_x000D_</oddHeader>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;11&amp;K000000 OFFICIAL - FOR PUBLIC RELEASE</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{dbf2ff9d-e249-40e2-b463-0b922d4f2f25}" enabled="1" method="Privileged" siteId="{fad277c9-c60a-4da1-b5f3-b3b8b34a82f9}" contentBits="3" removed="0"/>
+</clbl:labelList>
 </file>
--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmehta4\Repos\lsip_dashboard\Data\3-2_dataText\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C5C0B7E-8FE2-49C7-A70C-98E227F3E533}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
   <sheets>
     <sheet name="dataText" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="219">
   <si>
     <t>inactiveRate</t>
   </si>
@@ -686,9 +686,6 @@
     <t>&lt;a href = 'https://explore-education-statistics.service.gov.uk/find-statistics/16-18-destination-measures'&gt;16-18 destination measures&lt;/a&gt;</t>
   </si>
   <si>
-    <t>Jan-Dec 2024 data</t>
-  </si>
-  <si>
     <t>&lt;ol&gt;
   &lt;li&gt;These statistics should be treated as official statistics in development (previously known as experimental statistics), as they are still subject to testing the ability to meet user needs and may be modified in the future.&lt;/li&gt;
 &lt;li&gt;Where the same job is identified as being advertised through multiple adverts it is only counted once.&lt;/li&gt;
@@ -798,9 +795,6 @@
 &lt;/ol&gt;</t>
   </si>
   <si>
-    <t>Oct 2024 - Sep 2025</t>
-  </si>
-  <si>
     <t>&lt;a href = 'https://explore-education-statistics.service.gov.uk/find-statistics/key-stage-4-destination-measures/2023-24'&gt;Key stage 4 destination measures&lt;/a&gt;</t>
   </si>
   <si>
@@ -811,6 +805,9 @@
   </si>
   <si>
     <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data since October 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 and February 2026 data, and so some data has been suppressed in these months.</t>
+  </si>
+  <si>
+    <t>Jan 2025 - Dec 2025</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1290,7 @@
         <v>152</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -1334,7 +1331,7 @@
         <v>154</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>22</v>
@@ -1375,7 +1372,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>22</v>
@@ -1416,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>22</v>
@@ -1457,7 +1454,7 @@
         <v>153</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>22</v>
@@ -1498,7 +1495,7 @@
         <v>156</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>22</v>
@@ -1539,7 +1536,7 @@
         <v>157</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>22</v>
@@ -1580,7 +1577,7 @@
         <v>158</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
@@ -1621,10 +1618,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>167</v>
@@ -1633,7 +1630,7 @@
         <v>22</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>35</v>
@@ -1662,7 +1659,7 @@
         <v>3</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>23</v>
@@ -1703,7 +1700,7 @@
         <v>4</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>23</v>
@@ -1744,7 +1741,7 @@
         <v>5</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>23</v>
@@ -1785,19 +1782,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" t="s">
+        <v>209</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D14" t="s">
-        <v>210</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>39</v>
@@ -1826,19 +1823,19 @@
         <v>10</v>
       </c>
       <c r="B15" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>206</v>
-      </c>
       <c r="D15" t="s">
+        <v>209</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>40</v>
@@ -1867,19 +1864,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>41</v>
@@ -1908,19 +1905,19 @@
         <v>7</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D17" t="s">
         <v>209</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>42</v>
@@ -1948,8 +1945,8 @@
       <c r="A18" t="s">
         <v>160</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>194</v>
+      <c r="B18" s="10" t="s">
+        <v>218</v>
       </c>
       <c r="C18" t="s">
         <v>175</v>
@@ -1989,8 +1986,8 @@
       <c r="A19" t="s">
         <v>168</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>194</v>
+      <c r="B19" s="10" t="s">
+        <v>218</v>
       </c>
       <c r="C19" t="s">
         <v>175</v>
@@ -2034,13 +2031,13 @@
         <v>191</v>
       </c>
       <c r="C20" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>150</v>
@@ -2075,16 +2072,16 @@
         <v>191</v>
       </c>
       <c r="C21" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>193</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>45</v>
@@ -2113,7 +2110,7 @@
         <v>159</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C22" t="s">
         <v>22</v>
@@ -2137,7 +2134,7 @@
         <v>64</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>125</v>
@@ -2158,7 +2155,7 @@
         <v>26</v>
       </c>
       <c r="D23" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>18</v>
@@ -2179,7 +2176,7 @@
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>18</v>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C5C0B7E-8FE2-49C7-A70C-98E227F3E533}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C0C36F0-62C9-43FB-8465-A8623A0243A1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -801,13 +801,13 @@
     <t>&lt;a href='https://explore-education-statistics.service.gov.uk/find-statistics/further-education-and-skills/2024-25'&gt;Individualised Learner Record&lt;/a&gt;</t>
   </si>
   <si>
-    <t>February 2026 data</t>
-  </si>
-  <si>
-    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data since October 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 and February 2026 data, and so some data has been suppressed in these months.</t>
-  </si>
-  <si>
     <t>Jan 2025 - Dec 2025</t>
+  </si>
+  <si>
+    <t>April 2026 data</t>
+  </si>
+  <si>
+    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data since October 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 and February 2026 data, and so some data has been suppressed in these months. Finally, March 2026 data is currently supressed so is excluded from any three-month averages.</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1290,7 @@
         <v>152</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -1331,7 +1331,7 @@
         <v>154</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>22</v>
@@ -1372,7 +1372,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>22</v>
@@ -1413,7 +1413,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>22</v>
@@ -1454,7 +1454,7 @@
         <v>153</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>22</v>
@@ -1495,7 +1495,7 @@
         <v>156</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>22</v>
@@ -1536,7 +1536,7 @@
         <v>157</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>22</v>
@@ -1577,7 +1577,7 @@
         <v>158</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
@@ -1618,10 +1618,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>167</v>
@@ -1946,7 +1946,7 @@
         <v>160</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C18" t="s">
         <v>175</v>
@@ -1987,7 +1987,7 @@
         <v>168</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C19" t="s">
         <v>175</v>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C0C36F0-62C9-43FB-8465-A8623A0243A1}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7907F9B4-1A7A-4A91-B8DE-2231905DBF67}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -807,7 +807,7 @@
     <t>April 2026 data</t>
   </si>
   <si>
-    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data since October 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 and February 2026 data, and so some data has been suppressed in these months. Finally, March 2026 data is currently supressed so is excluded from any three-month averages.</t>
+    <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data since October 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 and February 2026 data, and so some data has been suppressed in these months. Finally,  the entirety of the March 2026 data is currently supressed so is excluded from any three-month averages.</t>
   </si>
 </sst>
 </file>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7907F9B4-1A7A-4A91-B8DE-2231905DBF67}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA7AE2E2-1E6D-4B40-B4F3-B154EFEE7D42}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -804,10 +804,10 @@
     <t>Jan 2025 - Dec 2025</t>
   </si>
   <si>
-    <t>April 2026 data</t>
-  </si>
-  <si>
     <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data since October 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 and February 2026 data, and so some data has been suppressed in these months. Finally,  the entirety of the March 2026 data is currently supressed so is excluded from any three-month averages.</t>
+  </si>
+  <si>
+    <t>May 2026 data</t>
   </si>
 </sst>
 </file>
@@ -1618,10 +1618,10 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>217</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>218</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>167</v>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA7AE2E2-1E6D-4B40-B4F3-B154EFEE7D42}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D49753A-6234-4368-B01E-36E67032C381}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -807,7 +807,7 @@
     <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data since October 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 and February 2026 data, and so some data has been suppressed in these months. Finally,  the entirety of the March 2026 data is currently supressed so is excluded from any three-month averages.</t>
   </si>
   <si>
-    <t>May 2026 data</t>
+    <t>June 2026 data</t>
   </si>
 </sst>
 </file>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D49753A-6234-4368-B01E-36E67032C381}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9250B018-2B86-44BF-9E5D-4DD6E1466454}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="230">
   <si>
     <t>inactiveRate</t>
   </si>
@@ -808,6 +808,47 @@
   </si>
   <si>
     <t>June 2026 data</t>
+  </si>
+  <si>
+    <t>apprenticeships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This indicator shows apprenticeship achievements. </t>
+  </si>
+  <si>
+    <t>Include all age apprenticeships.
+Apprenticeships are paid jobs that incorporate on-the-job and off-the-job training leading to nationally recognised qualifications.
+Achievements are the number of learners who successfully complete an individual aim in an academic year.</t>
+  </si>
+  <si>
+    <t>&lt;ol&gt;
+  &lt;li&gt;Total achievements is the count of learners that completed their qualification at any point during the stated academic period.&lt;/li&gt;
+ &lt;li&gt;Learners achieving more than one course will appear only once in the grand total.&lt;/li&gt;
+ &lt;li&gt;Years shown represent academic years.&lt;/li&gt;
+&lt;li&gt;Use caution when interpreting this data. A difference between subgroups does not necessarily imply any causality. There could be other contributing factors at work.&lt;/li&gt;
+&lt;li&gt;Figures for LSIP and CAs have been calculated from Local Authority District data to create a back series. There may be small differences to the published data for these geographies due to rounding errors.&lt;/li&gt;
+&lt;/ol&gt;</t>
+  </si>
+  <si>
+    <t>are apprenticeship volumes changing</t>
+  </si>
+  <si>
+    <t>The number of apprenticeships in</t>
+  </si>
+  <si>
+    <t>Apprenticeships</t>
+  </si>
+  <si>
+    <t>share of apprenticeships</t>
+  </si>
+  <si>
+    <t>Apprenticeships are</t>
+  </si>
+  <si>
+    <t>&lt;a href='https://explore-education-statistics.service.gov.uk/find-statistics/apprenticeships/2024-25'&gt;Individualised Learner Record&lt;/a&gt;</t>
+  </si>
+  <si>
+    <t>Apprenticeships in</t>
   </si>
 </sst>
 </file>
@@ -1236,7 +1277,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{49D33D53-EEC7-4B18-8C67-5F9034426AB5}">
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="25" style="6" customWidth="1"/>
@@ -2185,6 +2226,47 @@
         <v>149</v>
       </c>
       <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:13" ht="232.5" thickBot="1">
+      <c r="A25" t="s">
+        <v>219</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D25" t="s">
+        <v>228</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="G25" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>227</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9250B018-2B86-44BF-9E5D-4DD6E1466454}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4EA256D6-C674-4EEB-B0DB-876B1E2383E1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="229">
   <si>
     <t>inactiveRate</t>
   </si>
@@ -811,9 +811,6 @@
   </si>
   <si>
     <t>apprenticeships</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This indicator shows apprenticeship achievements. </t>
   </si>
   <si>
     <t>Include all age apprenticeships.
@@ -2234,38 +2231,36 @@
       <c r="B25" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="5"/>
+      <c r="D25" t="s">
+        <v>227</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="D25" t="s">
+      <c r="F25" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G25" s="8" t="s">
         <v>228</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F25" s="2" t="s">
+      <c r="H25" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="G25" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="H25" s="8" t="s">
+      <c r="I25" s="8" t="s">
         <v>223</v>
       </c>
-      <c r="I25" s="8" t="s">
+      <c r="J25" s="8" t="s">
         <v>224</v>
-      </c>
-      <c r="J25" s="8" t="s">
-        <v>225</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>219</v>
       </c>
       <c r="L25" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="M25" s="8" t="s">
         <v>226</v>
-      </c>
-      <c r="M25" s="8" t="s">
-        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D49753A-6234-4368-B01E-36E67032C381}"/>
+  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4ECAB5B-E0CA-4657-995B-16BBD11E023B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
@@ -807,7 +807,7 @@
     <t>These statistics should be treated as official statistics in development (previously known as experimental statistics). ONS have temporarily paused publication of the snapshot metric for online job adverts and so the dashboard currently shows the number of new adverts that have gone online in the month, presented as a three-month rolling average. The total across geographies may not sum to the England total. The data includes minor instances of suppression in June and July 2025 due to quality concerns. Where this has occurred, only the data containing no suppression is included in the rolling average. ONS have partially imputed the data since October 2025 in response to the source data presenting a larger level of duplicate adverts which are not being identified as such. As such, month-on-month trends during the affected period should be treated with caution. Additionally, a source of jobs was missing from the December 2025 and February 2026 data, and so some data has been suppressed in these months. Finally,  the entirety of the March 2026 data is currently supressed so is excluded from any three-month averages.</t>
   </si>
   <si>
-    <t>June 2026 data</t>
+    <t>July 2026 data</t>
   </si>
 </sst>
 </file>

--- a/Data/3-2_dataText/dataText.xlsx
+++ b/Data/3-2_dataText/dataText.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://educationgovuk-my.sharepoint.com/personal/paul_james_education_gov_uk/Documents/Documents/RProjects/lsip_dashboard/Data/3-2_dataText/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4ECAB5B-E0CA-4657-995B-16BBD11E023B}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{50BC6191-9AF8-4D14-B309-FB400C7A4CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2EF1EA43-A181-4023-B441-3C7796AC8001}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
+    <workbookView xWindow="1820" yWindow="20" windowWidth="20660" windowHeight="14300" xr2:uid="{E004AAF5-AC7D-409D-877C-9EBD23056743}"/>
   </bookViews>
   <sheets>
     <sheet name="dataText" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="220">
   <si>
     <t>inactiveRate</t>
   </si>
@@ -808,6 +808,9 @@
   </si>
   <si>
     <t>July 2026 data</t>
+  </si>
+  <si>
+    <t>April 2025 - Mar 2026</t>
   </si>
 </sst>
 </file>
@@ -1290,7 +1293,7 @@
         <v>152</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>22</v>
@@ -1331,7 +1334,7 @@
         <v>154</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>22</v>
@@ -1372,7 +1375,7 @@
         <v>155</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>22</v>
@@ -1413,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>22</v>
@@ -1454,7 +1457,7 @@
         <v>153</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>22</v>
@@ -1495,7 +1498,7 @@
         <v>156</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>22</v>
@@ -1536,7 +1539,7 @@
         <v>157</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>22</v>
@@ -1577,7 +1580,7 @@
         <v>158</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
